--- a/Result/profitability/3443.xlsx
+++ b/Result/profitability/3443.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.63</v>
       </c>
       <c r="M2" t="n">
-        <v>7.0075</v>
+        <v>7.495</v>
       </c>
       <c r="N2" t="n">
-        <v>27.6975</v>
+        <v>25.9175</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.67</v>
       </c>
       <c r="M3" t="n">
-        <v>6.2525</v>
+        <v>6.91375</v>
       </c>
       <c r="N3" t="n">
-        <v>25.715</v>
+        <v>24.25875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.66</v>
       </c>
       <c r="M4" t="n">
-        <v>5.67</v>
+        <v>6.225</v>
       </c>
       <c r="N4" t="n">
-        <v>24.10625</v>
+        <v>23.28875</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>1.32</v>
       </c>
       <c r="M5" t="n">
-        <v>4.93875</v>
+        <v>5.66125</v>
       </c>
       <c r="N5" t="n">
-        <v>23.20875</v>
+        <v>21.7375</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.95</v>
       </c>
       <c r="M6" t="n">
-        <v>4.32875</v>
+        <v>4.97125</v>
       </c>
       <c r="N6" t="n">
-        <v>22.22375</v>
+        <v>21.89</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.74</v>
       </c>
       <c r="M7" t="n">
-        <v>3.6125</v>
+        <v>3.982499999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>21.77625</v>
+        <v>22.09</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>2.6575</v>
+        <v>2.57375</v>
       </c>
       <c r="N8" t="n">
-        <v>21.95</v>
+        <v>21.24375</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3443</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>13897</v>
+      </c>
+      <c r="D75" t="n">
+        <v>10903</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2994</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1676</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>12.06%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>80</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1756</v>
+      </c>
+      <c r="K75" t="n">
+        <v>1555</v>
+      </c>
+      <c r="L75" t="n">
+        <v>11.61</v>
+      </c>
+      <c r="M75" t="n">
+        <v>8.255000000000001</v>
+      </c>
+      <c r="N75" t="n">
+        <v>27.80125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.6699999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.05456026058631924</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-5.649999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.207720588235294</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>5.779999999999999</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9914236706689536</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-11.77</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.3532412965186075</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
